--- a/artfynd/A 24737-2025 artfynd.xlsx
+++ b/artfynd/A 24737-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125757155</v>
       </c>
       <c r="B2" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24737-2025 artfynd.xlsx
+++ b/artfynd/A 24737-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125757155</v>
       </c>
       <c r="B2" t="n">
-        <v>91247</v>
+        <v>91248</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24737-2025 artfynd.xlsx
+++ b/artfynd/A 24737-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125757155</v>
       </c>
       <c r="B2" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24737-2025 artfynd.xlsx
+++ b/artfynd/A 24737-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125757155</v>
       </c>
       <c r="B2" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24737-2025 artfynd.xlsx
+++ b/artfynd/A 24737-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125757155</v>
       </c>
       <c r="B2" t="n">
-        <v>91254</v>
+        <v>91256</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24737-2025 artfynd.xlsx
+++ b/artfynd/A 24737-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125757155</v>
       </c>
       <c r="B2" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24737-2025 artfynd.xlsx
+++ b/artfynd/A 24737-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125757155</v>
       </c>
       <c r="B2" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 24737-2025 artfynd.xlsx
+++ b/artfynd/A 24737-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>126966992</v>
       </c>
       <c r="B4" t="n">
-        <v>58516</v>
+        <v>58520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24737-2025 artfynd.xlsx
+++ b/artfynd/A 24737-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>126966992</v>
       </c>
       <c r="B4" t="n">
-        <v>58520</v>
+        <v>58522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24737-2025 artfynd.xlsx
+++ b/artfynd/A 24737-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>126966992</v>
       </c>
       <c r="B4" t="n">
-        <v>58522</v>
+        <v>58516</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24737-2025 artfynd.xlsx
+++ b/artfynd/A 24737-2025 artfynd.xlsx
@@ -897,7 +897,7 @@
         <v>126966992</v>
       </c>
       <c r="B4" t="n">
-        <v>58516</v>
+        <v>58522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 24737-2025 artfynd.xlsx
+++ b/artfynd/A 24737-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125757155</v>
       </c>
       <c r="B2" t="n">
-        <v>91262</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126686774</v>
       </c>
       <c r="B3" t="n">
-        <v>58488</v>
+        <v>58790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>126966992</v>
       </c>
       <c r="B4" t="n">
-        <v>58522</v>
+        <v>58817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
